--- a/ig/DM-JUIN-2025/ASS-A14-FamilleActivite-ActiviteOperationnelle.xlsx
+++ b/ig/DM-JUIN-2025/ASS-A14-FamilleActivite-ActiviteOperationnelle.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
+    <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="141">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240531120000</t>
+    <t>20250627120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-31T12:00:00+01:00</t>
+    <t>2025-06-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -397,6 +398,45 @@
   </si>
   <si>
     <t>548</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R266-FamilleActiviteOperationnelleHorsSerafin/FHIR/TRE-R266-FamilleActiviteOperationnelleHorsSerafin</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>325</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>336</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>512</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>511</t>
+  </si>
+  <si>
+    <t>547</t>
   </si>
 </sst>
 </file>
@@ -1535,4 +1575,152 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>